--- a/FLORES DE ESTRADA/Abril/EDESUR ABRIL.xlsx
+++ b/FLORES DE ESTRADA/Abril/EDESUR ABRIL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Abril\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E53DECFD-4F49-48DE-A3FD-6B092F374FF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A5108F-3692-438C-A916-7F3198C1AA18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -603,6 +603,9 @@
     <xf numFmtId="165" fontId="4" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -612,9 +615,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -920,13 +920,13 @@
     <col min="3" max="3" width="14.85546875" customWidth="1"/>
     <col min="4" max="4" width="27" customWidth="1"/>
     <col min="5" max="5" width="6.5703125" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="10" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.7109375" customWidth="1"/>
     <col min="14" max="14" width="13.5703125" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="13.7109375" hidden="1" customWidth="1"/>
@@ -939,21 +939,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="57" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="56"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="59"/>
       <c r="N1" s="1"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
@@ -1670,7 +1670,7 @@
         <f>F18+195</f>
         <v>19713.599999999999</v>
       </c>
-      <c r="H18" s="61">
+      <c r="H18" s="56">
         <v>0</v>
       </c>
       <c r="I18" s="45">
@@ -1821,6 +1821,10 @@
         <f>C7*O20/100</f>
         <v>1598.0863744554051</v>
       </c>
+      <c r="S20">
+        <f>G20-F20</f>
+        <v>191.89999999999782</v>
+      </c>
     </row>
     <row r="21" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="37">
@@ -1832,7 +1836,7 @@
       <c r="C21" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="59" t="s">
+      <c r="D21" s="54" t="s">
         <v>64</v>
       </c>
       <c r="E21" s="37">
@@ -1845,7 +1849,7 @@
         <f>F21+302</f>
         <v>14348.5</v>
       </c>
-      <c r="H21" s="60">
+      <c r="H21" s="55">
         <v>0</v>
       </c>
       <c r="I21" s="39">
@@ -1908,7 +1912,7 @@
         <f>F22+193-30</f>
         <v>10672.2</v>
       </c>
-      <c r="H22" s="60">
+      <c r="H22" s="55">
         <v>0</v>
       </c>
       <c r="I22" s="39">
@@ -2517,7 +2521,7 @@
       <c r="C33" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="59" t="s">
+      <c r="D33" s="54" t="s">
         <v>64</v>
       </c>
       <c r="E33" s="37">
@@ -2603,19 +2607,19 @@
       <c r="A35" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="57" t="s">
+      <c r="C35" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="55"/>
-      <c r="E35" s="55"/>
-      <c r="F35" s="55"/>
-      <c r="G35" s="55"/>
-      <c r="H35" s="55"/>
-      <c r="I35" s="55"/>
-      <c r="J35" s="55"/>
-      <c r="K35" s="55"/>
-      <c r="L35" s="55"/>
-      <c r="M35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="58"/>
+      <c r="K35" s="58"/>
+      <c r="L35" s="58"/>
+      <c r="M35" s="61"/>
       <c r="N35" s="31"/>
       <c r="O35" s="2" t="e">
         <f t="shared" si="9"/>
@@ -6526,21 +6530,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="56"/>
+      <c r="A1" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="59"/>
       <c r="N1" s="1"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
@@ -8132,19 +8136,19 @@
       <c r="A35" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="57" t="s">
+      <c r="C35" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="55"/>
-      <c r="E35" s="55"/>
-      <c r="F35" s="55"/>
-      <c r="G35" s="55"/>
-      <c r="H35" s="55"/>
-      <c r="I35" s="55"/>
-      <c r="J35" s="55"/>
-      <c r="K35" s="55"/>
-      <c r="L35" s="55"/>
-      <c r="M35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="58"/>
+      <c r="K35" s="58"/>
+      <c r="L35" s="58"/>
+      <c r="M35" s="61"/>
       <c r="N35" s="31"/>
       <c r="O35" s="2" t="e">
         <f t="shared" si="8"/>
